--- a/utilities/genetic_diversity/genetic_diversity_r/models_summary.xlsx
+++ b/utilities/genetic_diversity/genetic_diversity_r/models_summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arimaite/Documents/GitHub/RSV-wastewater-2024-2025/utilities/genetic_diversity/genetic_diversity_r/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90353E11-3F27-A145-8927-653EF3441177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E0C1A3-EBDF-324E-96A2-6CD997BBC02E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="300" yWindow="600" windowWidth="28120" windowHeight="16360" xr2:uid="{4E21B9EB-94B6-5B47-B9B2-DB4ACE51F718}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16300" xr2:uid="{4E21B9EB-94B6-5B47-B9B2-DB4ACE51F718}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -47,9 +47,6 @@
     <t>Comparison</t>
   </si>
   <si>
-    <t>Subtype, whole genome</t>
-  </si>
-  <si>
     <t>Family (link)</t>
   </si>
   <si>
@@ -65,12 +62,6 @@
     <t>Gamma (log)</t>
   </si>
   <si>
-    <t>Subtype, F gene</t>
-  </si>
-  <si>
-    <t>Subtype, G gene</t>
-  </si>
-  <si>
     <t>F vs G, RSV-A</t>
   </si>
   <si>
@@ -80,10 +71,19 @@
     <t>Gene (F/G), log(mean coverage)</t>
   </si>
   <si>
-    <t>Entropy, nucleotide diversity</t>
-  </si>
-  <si>
-    <t>Entropy, nucleotide diversity, richness</t>
+    <t>Nucleotide diversity</t>
+  </si>
+  <si>
+    <t>Nucleotide diversity, richness</t>
+  </si>
+  <si>
+    <t>RSV-A vs RSV-B, whole genome</t>
+  </si>
+  <si>
+    <t>RSV-A vs RSV-B, F gene</t>
+  </si>
+  <si>
+    <t>RSV-A vs RSV-B, G gene</t>
   </si>
 </sst>
 </file>
@@ -746,10 +746,10 @@
   <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="44.33203125" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="38.83203125" customWidth="1"/>
     <col min="4" max="4" width="19.1640625" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
     <col min="6" max="6" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -769,16 +769,16 @@
         <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" s="17"/>
       <c r="H2" s="17"/>
@@ -786,19 +786,19 @@
     <row r="3" spans="1:8" ht="40" x14ac:dyDescent="0.3">
       <c r="A3" s="17"/>
       <c r="B3" s="6" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>1</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G3" s="17"/>
       <c r="H3" s="17"/>
@@ -806,19 +806,19 @@
     <row r="4" spans="1:8" ht="40" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="10" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>1</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G4" s="17"/>
       <c r="H4" s="17"/>
@@ -826,19 +826,19 @@
     <row r="5" spans="1:8" ht="40" x14ac:dyDescent="0.3">
       <c r="A5" s="17"/>
       <c r="B5" s="10" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>1</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G5" s="17"/>
       <c r="H5" s="17"/>
@@ -846,19 +846,19 @@
     <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.3">
       <c r="A6" s="17"/>
       <c r="B6" s="10" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>1</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G6" s="17"/>
       <c r="H6" s="17"/>
@@ -866,19 +866,19 @@
     <row r="7" spans="1:8" ht="61" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="17"/>
       <c r="B7" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>15</v>
-      </c>
       <c r="D7" s="15" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E7" s="15" t="s">
         <v>1</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G7" s="17"/>
       <c r="H7" s="17"/>
